--- a/Data/Rimify - Music Player & YouTube Sync - 3804662702/Rimify - Music Player & YouTube Sync - 3804662702.xlsx
+++ b/Data/Rimify - Music Player & YouTube Sync - 3804662702/Rimify - Music Player & YouTube Sync - 3804662702.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="373">
   <si>
     <t xml:space="preserve">Class+Node [(Identifier (Key)]</t>
   </si>
@@ -40,34 +40,142 @@
     <t xml:space="preserve">Korean (한국어) [Translation]</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Title</t>
+    <t xml:space="preserve">KeyBindingCategoryDef+Rimify_Controls.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingCategoryDef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Controls.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingCategoryDef+Rimify_Controls.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Controls.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music player playback controls / Горячие клавиши управления музыкальным плеером</t>
+  </si>
+  <si>
+    <t xml:space="preserve">음악 플레이어 재생 조작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingDef+Rimify_PlayPause.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingDef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_PlayPause.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play / Pause</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">재생 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">일시정지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingDef+Rimify_NextTrack.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_NextTrack.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next track</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 트랙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KeyBindingDef+Rimify_PrevTrack.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_PrevTrack.label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous track</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이전 트랙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Title</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed</t>
   </si>
   <si>
-    <t xml:space="preserve">RimTunes_Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Search</t>
+    <t xml:space="preserve">Rimify_Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Search</t>
   </si>
   <si>
     <t xml:space="preserve">Search:</t>
   </si>
   <si>
-    <t xml:space="preserve">검색</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_TracksFolder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_TracksFolder</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">검색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_TracksFolder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_TracksFolder</t>
   </si>
   <si>
     <t xml:space="preserve">Tracks Folder</t>
@@ -76,10 +184,10 @@
     <t xml:space="preserve">트랙 폴더</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Refresh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Refresh</t>
+    <t xml:space="preserve">Keyed+Rimify_Refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Refresh</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh</t>
@@ -88,22 +196,65 @@
     <t xml:space="preserve">새로고침</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_All</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_All</t>
+    <t xml:space="preserve">Keyed+Rimify_Refreshing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Refreshing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refreshing...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">새로고침 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">...</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">닫기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Cat_All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_All</t>
   </si>
   <si>
     <t xml:space="preserve">All Music</t>
   </si>
   <si>
-    <t xml:space="preserve">전체 음악</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Custom</t>
+    <t xml:space="preserve">모든 음악</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Custom</t>
   </si>
   <si>
     <t xml:space="preserve">My Tracks</t>
@@ -112,10 +263,10 @@
     <t xml:space="preserve">내 트랙</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Core</t>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Core</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Core</t>
   </si>
   <si>
     <t xml:space="preserve">Core &amp; DLC</t>
@@ -129,7 +280,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">본편 및 </t>
+      <t xml:space="preserve">코어 및 </t>
     </r>
     <r>
       <rPr>
@@ -143,10 +294,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Mods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Mods</t>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Mods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Mods</t>
   </si>
   <si>
     <t xml:space="preserve">Mods</t>
@@ -155,10 +306,10 @@
     <t xml:space="preserve">모드</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Peaceful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Peaceful</t>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Peaceful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Peaceful</t>
   </si>
   <si>
     <t xml:space="preserve">Peaceful</t>
@@ -167,10 +318,10 @@
     <t xml:space="preserve">평화</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Combat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Combat</t>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Combat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Combat</t>
   </si>
   <si>
     <t xml:space="preserve">Combat</t>
@@ -179,10 +330,10 @@
     <t xml:space="preserve">전투</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Cat_Disabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Cat_Disabled</t>
+    <t xml:space="preserve">Keyed+Rimify_Cat_Disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Cat_Disabled</t>
   </si>
   <si>
     <t xml:space="preserve">Disabled</t>
@@ -191,31 +342,31 @@
     <t xml:space="preserve">비활성화</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_PlaylistsHeader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_PlaylistsHeader</t>
+    <t xml:space="preserve">Keyed+Rimify_PlaylistsHeader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_PlaylistsHeader</t>
   </si>
   <si>
     <t xml:space="preserve">PLAYLISTS</t>
   </si>
   <si>
-    <t xml:space="preserve">플레이리스트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Col_Num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Col_Num</t>
+    <t xml:space="preserve">재생목록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Col_Num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Col_Num</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Col_Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Col_Title</t>
+    <t xml:space="preserve">Keyed+Rimify_Col_Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Col_Title</t>
   </si>
   <si>
     <t xml:space="preserve">TITLE</t>
@@ -224,10 +375,10 @@
     <t xml:space="preserve">제목</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Col_Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Col_Source</t>
+    <t xml:space="preserve">Keyed+Rimify_Col_Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Col_Source</t>
   </si>
   <si>
     <t xml:space="preserve">SOURCE</t>
@@ -236,10 +387,10 @@
     <t xml:space="preserve">출처</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Col_Tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Col_Tags</t>
+    <t xml:space="preserve">Keyed+Rimify_Col_Tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Col_Tags</t>
   </si>
   <si>
     <t xml:space="preserve">TAGS</t>
@@ -248,22 +399,22 @@
     <t xml:space="preserve">태그</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Col_Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Col_Time</t>
+    <t xml:space="preserve">Keyed+Rimify_Col_Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Col_Time</t>
   </si>
   <si>
     <t xml:space="preserve">TIME</t>
   </si>
   <si>
-    <t xml:space="preserve">재생 시간</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Source_Custom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Source_Custom</t>
+    <t xml:space="preserve">시간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Source_Custom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Source_Custom</t>
   </si>
   <si>
     <t xml:space="preserve">YouTube / Custom</t>
@@ -291,10 +442,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_RowPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_RowPlay</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RowPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RowPlay</t>
   </si>
   <si>
     <t xml:space="preserve">LMB: Play track
@@ -349,14 +500,14 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">플레이리스트 메뉴</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_ModeCombat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_ModeCombat</t>
+      <t xml:space="preserve">재생목록 메뉴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_ModeCombat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_ModeCombat</t>
   </si>
   <si>
     <t xml:space="preserve">Mode: Combat (click: switch to Peaceful)</t>
@@ -444,10 +595,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_ModePeaceful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_ModePeaceful</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_ModePeaceful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_ModePeaceful</t>
   </si>
   <si>
     <t xml:space="preserve">Mode: Peaceful (click: switch to Combat)</t>
@@ -535,10 +686,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_TimeOfDay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_TimeOfDay</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_TimeOfDay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_TimeOfDay</t>
   </si>
   <si>
     <t xml:space="preserve">Time of day: {0} (click: toggle)</t>
@@ -606,10 +757,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_RotAudible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_RotAudible</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RotAudible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RotAudible</t>
   </si>
   <si>
     <t xml:space="preserve">In game rotation (click: disable)</t>
@@ -623,7 +774,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">게임 내 재생 목록에 포함 </t>
+      <t xml:space="preserve">게임 내 순환 재생 </t>
     </r>
     <r>
       <rPr>
@@ -677,10 +828,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_RotMuted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_RotMuted</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RotMuted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RotMuted</t>
   </si>
   <si>
     <t xml:space="preserve">Excluded from rotation (click: enable)</t>
@@ -694,7 +845,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">게임 내 재생 목록에서 제외 </t>
+      <t xml:space="preserve">순환 재생에서 제외됨 </t>
     </r>
     <r>
       <rPr>
@@ -748,34 +899,34 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_AddToPlaylist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_AddToPlaylist</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_AddToPlaylist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_AddToPlaylist</t>
   </si>
   <si>
     <t xml:space="preserve">Add to playlist</t>
   </si>
   <si>
-    <t xml:space="preserve">플레이리스트에 추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_RemoveFromThisPlaylist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_RemoveFromThisPlaylist</t>
+    <t xml:space="preserve">재생목록에 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RemoveFromThisPlaylist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RemoveFromThisPlaylist</t>
   </si>
   <si>
     <t xml:space="preserve">Remove from this playlist</t>
   </si>
   <si>
-    <t xml:space="preserve">이 플레이리스트에서 제거</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Tip_DeleteTrack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Tip_DeleteTrack</t>
+    <t xml:space="preserve">이 재생목록에서 제거</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_DeleteTrack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_DeleteTrack</t>
   </si>
   <si>
     <t xml:space="preserve">Delete track from disk</t>
@@ -784,22 +935,22 @@
     <t xml:space="preserve">디스크에서 트랙 삭제</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_LockPlaylist_Off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_LockPlaylist_Off</t>
+    <t xml:space="preserve">Keyed+Rimify_LockPlaylist_Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_LockPlaylist_Off</t>
   </si>
   <si>
     <t xml:space="preserve">Play only this playlist</t>
   </si>
   <si>
-    <t xml:space="preserve">이 플레이리스트만 재생</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_LockPlaylist_On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_LockPlaylist_On</t>
+    <t xml:space="preserve">이 재생목록만 재생</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_LockPlaylist_On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_LockPlaylist_On</t>
   </si>
   <si>
     <t xml:space="preserve">Playing only this playlist (Active)</t>
@@ -813,7 +964,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">이 플레이리스트만 재생 중 </t>
+      <t xml:space="preserve">이 재생목록만 재생 중 </t>
     </r>
     <r>
       <rPr>
@@ -847,10 +998,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Menu_NoPlaylists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Menu_NoPlaylists</t>
+    <t xml:space="preserve">Keyed+Rimify_Menu_NoPlaylists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Menu_NoPlaylists</t>
   </si>
   <si>
     <t xml:space="preserve">No playlists (create via '+' on the left)</t>
@@ -864,7 +1015,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">플레이리스트가 없습니다 </t>
+      <t xml:space="preserve">재생목록 없음 </t>
     </r>
     <r>
       <rPr>
@@ -918,10 +1069,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Menu_RemoveFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Menu_RemoveFrom</t>
+    <t xml:space="preserve">Keyed+Rimify_Menu_RemoveFrom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Menu_RemoveFrom</t>
   </si>
   <si>
     <t xml:space="preserve">✓ Remove from: {0}</t>
@@ -949,10 +1100,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Menu_AddTo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Menu_AddTo</t>
+    <t xml:space="preserve">Keyed+Rimify_Menu_AddTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Menu_AddTo</t>
   </si>
   <si>
     <t xml:space="preserve">+ Add to: {0}</t>
@@ -980,10 +1131,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Menu_CreateNew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Menu_CreateNew</t>
+    <t xml:space="preserve">Keyed+Rimify_Menu_CreateNew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Menu_CreateNew</t>
   </si>
   <si>
     <t xml:space="preserve">+ Create new playlist...</t>
@@ -1007,7 +1158,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">새 플레이리스트 생성</t>
+      <t xml:space="preserve">새 재생목록 생성</t>
     </r>
     <r>
       <rPr>
@@ -1021,10 +1172,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Menu_DeleteTrack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Menu_DeleteTrack</t>
+    <t xml:space="preserve">Keyed+Rimify_Menu_DeleteTrack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Menu_DeleteTrack</t>
   </si>
   <si>
     <t xml:space="preserve">✕ Delete track from disk</t>
@@ -1033,22 +1184,22 @@
     <t xml:space="preserve">✕ 디스크에서 트랙 삭제</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Dlg_NewPlaylistTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Dlg_NewPlaylistTitle</t>
+    <t xml:space="preserve">Keyed+Rimify_Dlg_NewPlaylistTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Dlg_NewPlaylistTitle</t>
   </si>
   <si>
     <t xml:space="preserve">New Playlist</t>
   </si>
   <si>
-    <t xml:space="preserve">새 플레이리스트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Dlg_Create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Dlg_Create</t>
+    <t xml:space="preserve">새 재생목록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Dlg_Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Dlg_Create</t>
   </si>
   <si>
     <t xml:space="preserve">Create</t>
@@ -1057,10 +1208,10 @@
     <t xml:space="preserve">생성</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Dlg_Cancel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Dlg_Cancel</t>
+    <t xml:space="preserve">Keyed+Rimify_Dlg_Cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Dlg_Cancel</t>
   </si>
   <si>
     <t xml:space="preserve">Cancel</t>
@@ -1069,10 +1220,10 @@
     <t xml:space="preserve">취소</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Dlg_DeleteConfirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Dlg_DeleteConfirm</t>
+    <t xml:space="preserve">Keyed+Rimify_Dlg_DeleteConfirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Dlg_DeleteConfirm</t>
   </si>
   <si>
     <t xml:space="preserve">Delete playlist "{0}"?</t>
@@ -1086,7 +1237,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">플레이리스트 </t>
+      <t xml:space="preserve">재생목록 </t>
     </r>
     <r>
       <rPr>
@@ -1160,10 +1311,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Dlg_DeleteTrackConfirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Dlg_DeleteTrackConfirm</t>
+    <t xml:space="preserve">Keyed+Rimify_Dlg_DeleteTrackConfirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Dlg_DeleteTrackConfirm</t>
   </si>
   <si>
     <t xml:space="preserve">Permanently delete track "{0}"?</t>
@@ -1251,13 +1402,14 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Widget_Tip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Widget_Tip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMB: Open Rimify Player</t>
+    <t xml:space="preserve">Keyed+Rimify_Widget_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMB: open music library
+Hold LMB to drag and move widget</t>
   </si>
   <si>
     <r>
@@ -1278,24 +1430,44 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: Rimify Player </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">열기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Widget_PrevTip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Widget_PrevTip</t>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">음악 라이브러리 열기좌클릭 유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">위젯을 드래그하여 이동</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Widget_PrevTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_PrevTip</t>
   </si>
   <si>
     <t xml:space="preserve">Restart / Previous</t>
@@ -1329,14 +1501,14 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">이전 트랙</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Widget_PlayPauseTip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Widget_PlayPauseTip</t>
+      <t xml:space="preserve">이전</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Widget_PlayPauseTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_PlayPauseTip</t>
   </si>
   <si>
     <t xml:space="preserve">Pause / Play</t>
@@ -1374,22 +1546,130 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Widget_NextTip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Widget_NextTip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다음 트랙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Status_Paused</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Status_Paused</t>
+    <t xml:space="preserve">Keyed+Rimify_Widget_NextTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_NextTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_ToggleIcon_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_ToggleIcon_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify Music Player
+Playing: {0}
+LMB: Show/hide HUD player
+RMB: Open music library</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rimify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">음악 플레이어재생 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">좌클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: HUD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">숨기기우클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">음악 라이브러리 열기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Status_Paused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Status_Paused</t>
   </si>
   <si>
     <t xml:space="preserve">Paused</t>
@@ -1398,10 +1678,10 @@
     <t xml:space="preserve">일시정지됨</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Status_Waiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Status_Waiting</t>
+    <t xml:space="preserve">Keyed+Rimify_Status_Waiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Status_Waiting</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for music...</t>
@@ -1429,10 +1709,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Status_Silence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Status_Silence</t>
+    <t xml:space="preserve">Keyed+Rimify_Status_Silence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Status_Silence</t>
   </si>
   <si>
     <t xml:space="preserve">Silence...</t>
@@ -1460,10 +1740,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Status_Untitled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Status_Untitled</t>
+    <t xml:space="preserve">Keyed+Rimify_Status_Untitled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Status_Untitled</t>
   </si>
   <si>
     <t xml:space="preserve">Untitled</t>
@@ -1472,10 +1752,92 @@
     <t xml:space="preserve">제목 없음</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Time_Any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Time_Any</t>
+    <t xml:space="preserve">Keyed+Rimify_Status_SilenceTimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Status_SilenceTimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silence ({0}s)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">무음 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">({0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">초</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_VolumeTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_VolumeTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music Volume: {0}%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">음악 볼륨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {0}%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Time_Any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Time_Any</t>
   </si>
   <si>
     <t xml:space="preserve">Any</t>
@@ -1484,10 +1846,10 @@
     <t xml:space="preserve">모두</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Time_Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Time_Day</t>
+    <t xml:space="preserve">Keyed+Rimify_Time_Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Time_Day</t>
   </si>
   <si>
     <t xml:space="preserve">Day</t>
@@ -1496,10 +1858,10 @@
     <t xml:space="preserve">낮</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Time_Night</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Time_Night</t>
+    <t xml:space="preserve">Keyed+Rimify_Time_Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Time_Night</t>
   </si>
   <si>
     <t xml:space="preserve">Night</t>
@@ -1508,81 +1870,19 @@
     <t xml:space="preserve">밤</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Btn_DownloadYT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Btn_DownloadYT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_DialogTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_DialogTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Download from YouTube</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">YouTube</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">에서 다운로드</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_UrlLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_UrlLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Video or YouTube Music URL:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">동영상 또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">YouTube Music URL:</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_BtnDownload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_BtnDownload</t>
+    <t xml:space="preserve">Keyed+Rimify_DownloadSection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_DownloadSection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_DownloadBtn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_DownloadBtn</t>
   </si>
   <si>
     <t xml:space="preserve">Download</t>
@@ -1591,40 +1891,31 @@
     <t xml:space="preserve">다운로드</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_BtnCancel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_BtnCancel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_CombatPreset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_CombatPreset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag as Combat track</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전투 트랙으로 지정</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_Idle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_Idle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">준비 완료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_PreparingTool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_PreparingTool</t>
+    <t xml:space="preserve">Keyed+Rimify_DownloadingToolbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_DownloadingToolbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0} ({1}%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_YT_CombatPreset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_CombatPreset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combat track</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전투 트랙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_PreparingTool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_PreparingTool</t>
   </si>
   <si>
     <t xml:space="preserve">Downloading yt-dlp core...</t>
@@ -1662,10 +1953,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_DownloadingFfmpeg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_DownloadingFfmpeg</t>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_DownloadingFfmpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_DownloadingFfmpeg</t>
   </si>
   <si>
     <t xml:space="preserve">Downloading FFmpeg...</t>
@@ -1703,10 +1994,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_Downloading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_Downloading</t>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_Downloading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_Downloading</t>
   </si>
   <si>
     <t xml:space="preserve">Downloading audio stream...</t>
@@ -1734,10 +2025,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_Converting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_Converting</t>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_Converting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_Converting</t>
   </si>
   <si>
     <t xml:space="preserve">Converting to MP3...</t>
@@ -1775,10 +2066,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_Success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_Success</t>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_Success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_Success</t>
   </si>
   <si>
     <t xml:space="preserve">Download completed successfully!</t>
@@ -1806,10 +2097,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_YT_Status_Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_YT_Status_Error</t>
+    <t xml:space="preserve">Keyed+Rimify_YT_Status_Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Status_Error</t>
   </si>
   <si>
     <t xml:space="preserve">Error occurred during download</t>
@@ -1818,30 +2109,860 @@
     <t xml:space="preserve">다운로드 중 오류가 발생했습니다</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+Rimify_Refresh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_Refresh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+Rimify_Refreshing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_Refreshing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refreshing...</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">새로고침 중</t>
+    <t xml:space="preserve">Keyed+Rimify_Setting_ContinuousMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_ContinuousMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuous Playback (Non-stop)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">연속 재생 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">중단 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_ContinuousMode_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_ContinuousMode_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enabled: tracks play back-to-back without pauses.
+Disabled: keeps an atmospheric 1–3 min pause between songs like vanilla RimWorld (pauses are skipped during combat).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">활성화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">트랙을 중단 없이 연속으로 재생합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">비활성화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">바닐라 림월드처럼 곡 사이에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1~3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">분의 분위기 있는 공백을 유지합니다 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">전투 중에는 공백이 생략됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_ContinuousMode_Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_ContinuousMode_Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pauses between tracks (1–3 min): ON (click: toggle non-stop)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">트랙 사이 공백 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1~3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">켜짐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">연속 재생으로 전환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Settings_Hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Settings_Hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click the button below to open your music library, configure track rotation and playlists:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">아래 버튼을 클릭하여 음악 라이브러리를 열고 트랙 순환 및 재생목록을 설정하십시오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Btn_OpenManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Btn_OpenManager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Rimify Player</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rimify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 열기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_MenuMusicFolder_Btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_MenuMusicFolder_Btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menu music folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메뉴 음악 폴더</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_MenuMusicFolder_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_MenuMusicFolder_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open menu music folder (Sounds/Music). Place your audio file named MenuSong (.ogg, .mp3, or .wav) here.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">메뉴 음악 폴더 열기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Sounds/Music). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이곳에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MenuSong</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이라는 이름의 오디오 파일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(.ogg, .mp3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.wav)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">을 넣으십시오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_PauseHeader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_PauseHeader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanilla Pause Intervals (Atmospheric Silence):</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">바닐라 공백 시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">분위기 있는 무음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">):</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_MinPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_MinPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min pause: {0}s</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">최소 공백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">초</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_MaxPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_MaxPause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max pause: {0}s</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">최대 공백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: {0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">초</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_ResetWidget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_ResetWidget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset HUD Widget Position</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HUD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">위젯 위치 초기화</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_ResetWidget_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_ResetWidget_Tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restores the floating player back to the top-right corner of the screen.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플로팅 플레이어를 화면 오른쪽 위 모서리로 되돌립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_Stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_Stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media library: {0} tracks registered, {1} custom playlists.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">미디어 라이브러리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">트랙 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">개 등록됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">사용자 지정 재생목록 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">{1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_YT_BtnUpdate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_BtnUpdate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update yt-dlp core (-U)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">yt-dlp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">코어 업데이트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-U)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_YT_Updating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_YT_Updating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updating yt-dlp core...</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">yt-dlp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">코어 업데이트 중</t>
     </r>
     <r>
       <rPr>
@@ -1855,60 +2976,168 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+Rimify_DownloadSection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_DownloadSection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+Rimify_DownloadBtn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_DownloadBtn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+Rimify_DownloadingToolbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_DownloadingToolbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0} ({1}%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+Rimify_Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rimify_Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">닫기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Setting_ContinuousMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Setting_ContinuousMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continuous Playback (Non-stop)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">연속 재생 </t>
+    <t xml:space="preserve">Keyed+Rimify_Widget_NoteTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_NoteTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMB: Open Rimify Player
+RMB: Collapse to mini-icon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">좌클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Rimify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 열기우클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">미니 아이콘으로 축소</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Widget_MiniTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Widget_MiniTip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMB: Open Rimify Player
+RMB: Expand full widget</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">좌클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Rimify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 열기우클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">전체 위젯으로 확장</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_ShuffleOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_ShuffleOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle mode: ON (click: play sequentially)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">셔플 모드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">켜짐 </t>
     </r>
     <r>
       <rPr>
@@ -1928,7 +3157,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">무정지</t>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">순차 재생</t>
     </r>
     <r>
       <rPr>
@@ -1942,24 +3191,24 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Keyed+RimTunes_Setting_ContinuousMode_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Setting_ContinuousMode_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enabled: tracks play back-to-back without pauses.\nDisabled: keeps an atmospheric 1–3 min pause between songs like vanilla RimWorld (pauses are skipped during combat).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">활성화</t>
+    <t xml:space="preserve">Keyed+Rimify_Tip_ShuffleOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_ShuffleOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shuffle mode: OFF (click: randomize playback)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">셔플 모드</t>
     </r>
     <r>
       <rPr>
@@ -1979,7 +3228,292 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">트랙 사이에 일시정지 없이 연속으로 재생합니다</t>
+      <t xml:space="preserve">꺼짐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">무작위 재생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RepeatOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RepeatOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat track: ON (click: repeat off)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">트랙 반복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">켜짐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">반복 끄기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Tip_RepeatOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Tip_RepeatOff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repeat track: OFF (click: repeat current track)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">트랙 반복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">꺼짐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">클릭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">현재 트랙 반복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_CustomMenuMusic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_CustomMenuMusic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace main menu music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 메뉴 음악 교체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyed+Rimify_Setting_CustomMenuMusic_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rimify_Setting_CustomMenuMusic_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play your custom track from the MenuMusic folder instead of the default RimWorld theme.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기본 림월드 테마 대신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MenuMusic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">폴더의 사용자 지정 트랙을 재생합니다</t>
     </r>
     <r>
       <rPr>
@@ -1990,310 +3524,6 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">비활성화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">바닐라 림월드처럼 곡 사이에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1~3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">분간 분위기 전환을 위한 무음 구간을 유지합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">전투 중에는 일시정지를 건너뜁니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Status_SilenceTimer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Status_SilenceTimer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silence ({0}s)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">무음 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">({0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">초</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Settings_Hint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Settings_Hint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click the button below to open your music library, configure track rotation and playlists:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">아래 버튼을 클릭하여 음악 라이브러리를 열고 트랙 재생 목록과 플레이리스트를 설정할 수 있습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Btn_OpenManager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Btn_OpenManager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Rimify Player</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rimify Player </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">열기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Keyed+RimTunes_Setting_ContinuousMode_Off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RimTunes_Setting_ContinuousMode_Off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pauses between tracks (1–3 min): ON (click: toggle non-stop)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">트랙 사이 일시정지 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1~3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">분</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">): </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">켜짐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">클릭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">연속 재생으로 전환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
     </r>
   </si>
 </sst>
@@ -2340,6 +3570,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="129"/>
@@ -2351,13 +3588,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2402,7 +3632,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2411,7 +3641,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2419,12 +3657,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2619,14 +3857,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr defaultColWidth="8.390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="47.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="78.46"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="8.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="42.86"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="8.39"/>
   </cols>
   <sheetData>
@@ -2643,14 +3878,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2660,14 +3895,14 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2677,1472 +3912,1921 @@
       <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="0"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="0"/>
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="0"/>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="0"/>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="0"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="0"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="0"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="0"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="0"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="0"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="0"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="0"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="0"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="0"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="0"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="0"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="0"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="0"/>
+        <v>57</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="0"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="0"/>
+      <c r="F15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="0"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="0"/>
+      <c r="F16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="0"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="0"/>
+      <c r="F17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="0"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="0"/>
+      <c r="F18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="0"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="0"/>
+      <c r="F19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="0"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="0"/>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="0"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="0"/>
+      <c r="F21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="0"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="0"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="0"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="0"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G24" s="0"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="0"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="0"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="0"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="0"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="0"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G27" s="0"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="0"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="0"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="0"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G29" s="0"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="0"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G30" s="0"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="0"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="0"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="0"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G32" s="0"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="0"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G33" s="0"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="0"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G34" s="0"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="0"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G35" s="0"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="0"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G36" s="0"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="0"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G37" s="0"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="0"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G38" s="0"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="0"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G39" s="0"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="0"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="0"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="0"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="0"/>
+      <c r="J41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="0"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="0"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>169</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="0"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="0"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="0"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="0"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="0"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>181</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="0"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="0"/>
-    </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>189</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="0"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>193</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="H49" s="2"/>
-      <c r="I49" s="0"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>197</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="0"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="B52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="0"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="F52" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="H52" s="2"/>
-      <c r="I52" s="0"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="0"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="7"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H54" s="2"/>
-      <c r="I54" s="0"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="E55" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H55" s="2"/>
-      <c r="I55" s="0"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H56" s="2"/>
-      <c r="I56" s="0"/>
+      <c r="F56" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E57" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="0"/>
+      <c r="F57" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E58" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="0"/>
+      <c r="F58" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E59" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="E59" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G59" s="2"/>
-      <c r="H59" s="0"/>
+      <c r="F59" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E60" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="E60" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G60" s="2"/>
-      <c r="H60" s="0"/>
+      <c r="F60" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E61" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="G61" s="2"/>
-      <c r="H61" s="0"/>
+      <c r="F61" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E62" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="E62" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G62" s="2"/>
-      <c r="H62" s="0"/>
+      <c r="F62" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="G63" s="2"/>
-      <c r="H63" s="0"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G64" s="2"/>
-      <c r="H64" s="0"/>
+      <c r="F64" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="1" t="s">
+      <c r="E65" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65" s="2"/>
-      <c r="H65" s="0"/>
+      <c r="F65" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E66" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G66" s="2"/>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E67" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G67" s="2"/>
-      <c r="H67" s="0"/>
+      <c r="E67" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G68" s="2"/>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>266</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G69" s="2"/>
-      <c r="H69" s="0"/>
+        <v>270</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="0"/>
+        <v>274</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="G71" s="0"/>
-      <c r="H71" s="0"/>
-      <c r="I71" s="0"/>
-      <c r="J71" s="0"/>
-    </row>
-    <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>278</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G72" s="0"/>
-      <c r="H72" s="0"/>
-      <c r="I72" s="0"/>
-      <c r="J72" s="0"/>
-    </row>
-    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>282</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G73" s="0"/>
-      <c r="H73" s="0"/>
-      <c r="I73" s="0"/>
-      <c r="J73" s="0"/>
+        <v>286</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-      <c r="I74" s="0"/>
-      <c r="J74" s="0"/>
-    </row>
-    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>290</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G75" s="0"/>
-      <c r="H75" s="0"/>
-      <c r="I75" s="0"/>
-      <c r="J75" s="0"/>
+        <v>294</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G76" s="2"/>
-      <c r="H76" s="0"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G77" s="2"/>
-      <c r="H77" s="0"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I78" s="2"/>
-      <c r="J78" s="0"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I79" s="2"/>
-      <c r="J79" s="0"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I80" s="2"/>
-      <c r="J80" s="0"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I81" s="2"/>
-      <c r="J81" s="0"/>
+        <v>298</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="78" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" customFormat="false" ht="42.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L117" s="3"/>
+      <c r="M117" s="3"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L118" s="3"/>
+      <c r="M118" s="3"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L129" s="3"/>
+      <c r="M129" s="3"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
